--- a/Project Governance/v3/gantt-v2.xlsx
+++ b/Project Governance/v3/gantt-v2.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="d mmm"/>
     <numFmt numFmtId="165" formatCode="dd mmm"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,8 +77,14 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+      <color rgb="00607D8B"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -138,6 +144,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00ECEFF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001769AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B95A3"/>
       </patternFill>
     </fill>
   </fills>
@@ -240,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -347,76 +373,55 @@
     <xf numFmtId="164" fontId="8" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -927,7 +932,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1004,7 +1009,7 @@
       <c r="N4" s="38" t="n"/>
       <c r="O4" s="9" t="inlineStr">
         <is>
-          <t>ACTIVE COMPLETE</t>
+          <t>ACTIVE PROGRESS</t>
         </is>
       </c>
       <c r="P4" s="38" t="n"/>
@@ -1012,36 +1017,36 @@
     <row r="5">
       <c r="A5" s="10">
         <f>COUNTIF($F$9:$F$35,"Done")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="B5" s="37" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="10">
         <f>COUNTIF($F$9:$F$35,"Review")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="E5" s="37" t="n"/>
       <c r="F5" s="38" t="n"/>
       <c r="G5" s="10">
         <f>COUNTIF($F$9:$F$35,"Doing")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="H5" s="37" t="n"/>
       <c r="I5" s="38" t="n"/>
       <c r="J5" s="10">
         <f>COUNTIF($F$9:$F$35,"To Do")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K5" s="37" t="n"/>
       <c r="L5" s="38" t="n"/>
       <c r="M5" s="10">
         <f>COUNTIF($F$9:$F$35,"Deferred")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N5" s="38" t="n"/>
       <c r="O5" s="11">
         <f>COUNTIF($F$9:$F$35,"Done")/COUNTIF($F$9:$F$35,"&lt;&gt;Deferred")</f>
-        <v/>
+        <v>0.2692307692307692</v>
       </c>
       <c r="P5" s="38" t="n"/>
     </row>
@@ -1165,30 +1170,30 @@
       <c r="K9" s="47" t="n"/>
       <c r="L9" s="47" t="n"/>
       <c r="M9" s="47" t="n"/>
-      <c r="N9" s="48" t="n"/>
+      <c r="N9" s="47" t="n"/>
       <c r="O9" s="47" t="n"/>
       <c r="P9" s="47" t="n"/>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="48" t="inlineStr">
         <is>
           <t>GOV-02</t>
         </is>
       </c>
-      <c r="B10" s="50" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>Requirements and governance baseline</t>
         </is>
       </c>
-      <c r="C10" s="50" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>Tamer (A); Nick and Dan (R)</t>
         </is>
       </c>
-      <c r="D10" s="51" t="n">
+      <c r="D10" s="50" t="n">
         <v>46182</v>
       </c>
-      <c r="E10" s="51" t="n">
+      <c r="E10" s="50" t="n">
         <v>46194</v>
       </c>
       <c r="F10" s="45" t="inlineStr">
@@ -1203,7 +1208,7 @@
       <c r="K10" s="47" t="n"/>
       <c r="L10" s="47" t="n"/>
       <c r="M10" s="47" t="n"/>
-      <c r="N10" s="48" t="n"/>
+      <c r="N10" s="47" t="n"/>
       <c r="O10" s="47" t="n"/>
       <c r="P10" s="47" t="n"/>
     </row>
@@ -1229,42 +1234,42 @@
       <c r="E11" s="44" t="n">
         <v>46248</v>
       </c>
-      <c r="F11" s="52" t="inlineStr">
+      <c r="F11" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
       </c>
-      <c r="G11" s="53" t="n"/>
-      <c r="H11" s="53" t="n"/>
-      <c r="I11" s="53" t="n"/>
-      <c r="J11" s="53" t="n"/>
-      <c r="K11" s="53" t="n"/>
-      <c r="L11" s="53" t="n"/>
-      <c r="M11" s="53" t="n"/>
-      <c r="N11" s="54" t="n"/>
-      <c r="O11" s="53" t="n"/>
-      <c r="P11" s="53" t="n"/>
+      <c r="G11" s="52" t="n"/>
+      <c r="H11" s="52" t="n"/>
+      <c r="I11" s="52" t="n"/>
+      <c r="J11" s="52" t="n"/>
+      <c r="K11" s="52" t="n"/>
+      <c r="L11" s="52" t="n"/>
+      <c r="M11" s="52" t="n"/>
+      <c r="N11" s="52" t="n"/>
+      <c r="O11" s="52" t="n"/>
+      <c r="P11" s="52" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="49" t="inlineStr">
+      <c r="A12" s="48" t="inlineStr">
         <is>
           <t>STR-01</t>
         </is>
       </c>
-      <c r="B12" s="50" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>Market research</t>
         </is>
       </c>
-      <c r="C12" s="50" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>Tamer (A/R); Conrad and Mo (C)</t>
         </is>
       </c>
-      <c r="D12" s="51" t="n">
+      <c r="D12" s="50" t="n">
         <v>46204</v>
       </c>
-      <c r="E12" s="51" t="n">
+      <c r="E12" s="50" t="n">
         <v>46210</v>
       </c>
       <c r="F12" s="45" t="inlineStr">
@@ -1277,9 +1282,9 @@
       <c r="I12" s="47" t="n"/>
       <c r="J12" s="46" t="n"/>
       <c r="K12" s="46" t="n"/>
-      <c r="L12" s="46" t="n"/>
-      <c r="M12" s="46" t="n"/>
-      <c r="N12" s="55" t="n"/>
+      <c r="L12" s="47" t="n"/>
+      <c r="M12" s="47" t="n"/>
+      <c r="N12" s="47" t="n"/>
       <c r="O12" s="47" t="n"/>
       <c r="P12" s="47" t="n"/>
     </row>
@@ -1313,34 +1318,34 @@
       <c r="G13" s="47" t="n"/>
       <c r="H13" s="47" t="n"/>
       <c r="I13" s="47" t="n"/>
-      <c r="J13" s="46" t="n"/>
+      <c r="J13" s="47" t="n"/>
       <c r="K13" s="46" t="n"/>
       <c r="L13" s="46" t="n"/>
-      <c r="M13" s="46" t="n"/>
-      <c r="N13" s="55" t="n"/>
+      <c r="M13" s="47" t="n"/>
+      <c r="N13" s="47" t="n"/>
       <c r="O13" s="47" t="n"/>
       <c r="P13" s="47" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="49" t="inlineStr">
+      <c r="A14" s="48" t="inlineStr">
         <is>
           <t>STR-03</t>
         </is>
       </c>
-      <c r="B14" s="50" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>Strategic planning</t>
         </is>
       </c>
-      <c r="C14" s="50" t="inlineStr">
+      <c r="C14" s="49" t="inlineStr">
         <is>
           <t>Tamer (A/R); all leads (C)</t>
         </is>
       </c>
-      <c r="D14" s="51" t="n">
+      <c r="D14" s="50" t="n">
         <v>46218</v>
       </c>
-      <c r="E14" s="51" t="n">
+      <c r="E14" s="50" t="n">
         <v>46224</v>
       </c>
       <c r="F14" s="45" t="inlineStr">
@@ -1351,11 +1356,11 @@
       <c r="G14" s="47" t="n"/>
       <c r="H14" s="47" t="n"/>
       <c r="I14" s="47" t="n"/>
-      <c r="J14" s="46" t="n"/>
-      <c r="K14" s="46" t="n"/>
+      <c r="J14" s="47" t="n"/>
+      <c r="K14" s="47" t="n"/>
       <c r="L14" s="46" t="n"/>
       <c r="M14" s="46" t="n"/>
-      <c r="N14" s="55" t="n"/>
+      <c r="N14" s="47" t="n"/>
       <c r="O14" s="47" t="n"/>
       <c r="P14" s="47" t="n"/>
     </row>
@@ -1381,7 +1386,7 @@
       <c r="E15" s="44" t="n">
         <v>46234</v>
       </c>
-      <c r="F15" s="45" t="inlineStr">
+      <c r="F15" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
@@ -1389,34 +1394,34 @@
       <c r="G15" s="47" t="n"/>
       <c r="H15" s="47" t="n"/>
       <c r="I15" s="47" t="n"/>
-      <c r="J15" s="46" t="n"/>
-      <c r="K15" s="46" t="n"/>
-      <c r="L15" s="46" t="n"/>
-      <c r="M15" s="46" t="n"/>
-      <c r="N15" s="55" t="n"/>
+      <c r="J15" s="52" t="n"/>
+      <c r="K15" s="52" t="n"/>
+      <c r="L15" s="52" t="n"/>
+      <c r="M15" s="52" t="n"/>
+      <c r="N15" s="52" t="n"/>
       <c r="O15" s="47" t="n"/>
       <c r="P15" s="47" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="49" t="inlineStr">
+      <c r="A16" s="48" t="inlineStr">
         <is>
           <t>PRD-01</t>
         </is>
       </c>
-      <c r="B16" s="50" t="inlineStr">
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>Product workflow and release rules</t>
         </is>
       </c>
-      <c r="C16" s="50" t="inlineStr">
+      <c r="C16" s="49" t="inlineStr">
         <is>
           <t>Dan (A/R); Nick (R)</t>
         </is>
       </c>
-      <c r="D16" s="51" t="n">
+      <c r="D16" s="50" t="n">
         <v>46182</v>
       </c>
-      <c r="E16" s="51" t="n">
+      <c r="E16" s="50" t="n">
         <v>46213</v>
       </c>
       <c r="F16" s="45" t="inlineStr">
@@ -1431,7 +1436,7 @@
       <c r="K16" s="46" t="n"/>
       <c r="L16" s="47" t="n"/>
       <c r="M16" s="47" t="n"/>
-      <c r="N16" s="48" t="n"/>
+      <c r="N16" s="47" t="n"/>
       <c r="O16" s="47" t="n"/>
       <c r="P16" s="47" t="n"/>
     </row>
@@ -1457,42 +1462,42 @@
       <c r="E17" s="44" t="n">
         <v>46246</v>
       </c>
-      <c r="F17" s="56" t="inlineStr">
+      <c r="F17" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
       </c>
       <c r="G17" s="47" t="n"/>
       <c r="H17" s="47" t="n"/>
-      <c r="I17" s="57" t="n"/>
-      <c r="J17" s="57" t="n"/>
-      <c r="K17" s="57" t="n"/>
-      <c r="L17" s="57" t="n"/>
-      <c r="M17" s="57" t="n"/>
-      <c r="N17" s="58" t="n"/>
-      <c r="O17" s="57" t="n"/>
-      <c r="P17" s="57" t="n"/>
+      <c r="I17" s="52" t="n"/>
+      <c r="J17" s="52" t="n"/>
+      <c r="K17" s="52" t="n"/>
+      <c r="L17" s="52" t="n"/>
+      <c r="M17" s="52" t="n"/>
+      <c r="N17" s="52" t="n"/>
+      <c r="O17" s="52" t="n"/>
+      <c r="P17" s="52" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="49" t="inlineStr">
+      <c r="A18" s="48" t="inlineStr">
         <is>
           <t>TEC-01</t>
         </is>
       </c>
-      <c r="B18" s="50" t="inlineStr">
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>Smart contract and contract tests</t>
         </is>
       </c>
-      <c r="C18" s="50" t="inlineStr">
+      <c r="C18" s="49" t="inlineStr">
         <is>
           <t>Nick (A/R); Dan (R)</t>
         </is>
       </c>
-      <c r="D18" s="51" t="n">
+      <c r="D18" s="50" t="n">
         <v>46188</v>
       </c>
-      <c r="E18" s="51" t="n">
+      <c r="E18" s="50" t="n">
         <v>46213</v>
       </c>
       <c r="F18" s="45" t="inlineStr">
@@ -1507,7 +1512,7 @@
       <c r="K18" s="46" t="n"/>
       <c r="L18" s="47" t="n"/>
       <c r="M18" s="47" t="n"/>
-      <c r="N18" s="48" t="n"/>
+      <c r="N18" s="47" t="n"/>
       <c r="O18" s="47" t="n"/>
       <c r="P18" s="47" t="n"/>
     </row>
@@ -1533,45 +1538,45 @@
       <c r="E19" s="44" t="n">
         <v>46239</v>
       </c>
-      <c r="F19" s="45" t="inlineStr">
+      <c r="F19" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
       </c>
       <c r="G19" s="47" t="n"/>
       <c r="H19" s="47" t="n"/>
-      <c r="I19" s="46" t="n"/>
-      <c r="J19" s="46" t="n"/>
-      <c r="K19" s="46" t="n"/>
-      <c r="L19" s="46" t="n"/>
-      <c r="M19" s="46" t="n"/>
-      <c r="N19" s="55" t="n"/>
-      <c r="O19" s="46" t="n"/>
+      <c r="I19" s="52" t="n"/>
+      <c r="J19" s="52" t="n"/>
+      <c r="K19" s="52" t="n"/>
+      <c r="L19" s="52" t="n"/>
+      <c r="M19" s="52" t="n"/>
+      <c r="N19" s="52" t="n"/>
+      <c r="O19" s="52" t="n"/>
       <c r="P19" s="47" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="49" t="inlineStr">
+      <c r="A20" s="48" t="inlineStr">
         <is>
           <t>TEC-03</t>
         </is>
       </c>
-      <c r="B20" s="50" t="inlineStr">
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>Testnet deployment and onboarding gate</t>
         </is>
       </c>
-      <c r="C20" s="50" t="inlineStr">
+      <c r="C20" s="49" t="inlineStr">
         <is>
           <t>Nick (A); Dan (R)</t>
         </is>
       </c>
-      <c r="D20" s="51" t="n">
+      <c r="D20" s="50" t="n">
         <v>46203</v>
       </c>
-      <c r="E20" s="51" t="n">
+      <c r="E20" s="50" t="n">
         <v>46244</v>
       </c>
-      <c r="F20" s="45" t="inlineStr">
+      <c r="F20" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
@@ -1579,13 +1584,13 @@
       <c r="G20" s="47" t="n"/>
       <c r="H20" s="47" t="n"/>
       <c r="I20" s="47" t="n"/>
-      <c r="J20" s="46" t="n"/>
-      <c r="K20" s="46" t="n"/>
-      <c r="L20" s="46" t="n"/>
-      <c r="M20" s="46" t="n"/>
-      <c r="N20" s="55" t="n"/>
-      <c r="O20" s="46" t="n"/>
-      <c r="P20" s="46" t="n"/>
+      <c r="J20" s="52" t="n"/>
+      <c r="K20" s="52" t="n"/>
+      <c r="L20" s="52" t="n"/>
+      <c r="M20" s="52" t="n"/>
+      <c r="N20" s="52" t="n"/>
+      <c r="O20" s="52" t="n"/>
+      <c r="P20" s="52" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="42" t="inlineStr">
@@ -1609,7 +1614,7 @@
       <c r="E21" s="44" t="n">
         <v>46246</v>
       </c>
-      <c r="F21" s="56" t="inlineStr">
+      <c r="F21" s="53" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
@@ -1621,46 +1626,46 @@
       <c r="K21" s="47" t="n"/>
       <c r="L21" s="47" t="n"/>
       <c r="M21" s="47" t="n"/>
-      <c r="N21" s="48" t="n"/>
-      <c r="O21" s="57" t="n"/>
-      <c r="P21" s="57" t="n"/>
+      <c r="N21" s="47" t="n"/>
+      <c r="O21" s="54" t="n"/>
+      <c r="P21" s="54" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="49" t="inlineStr">
+      <c r="A22" s="48" t="inlineStr">
         <is>
           <t>UX-01</t>
         </is>
       </c>
-      <c r="B22" s="50" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>Role journeys and consolidated dashboard</t>
         </is>
       </c>
-      <c r="C22" s="50" t="inlineStr">
+      <c r="C22" s="49" t="inlineStr">
         <is>
           <t>Mo (A/R); Nick and Dan (C)</t>
         </is>
       </c>
-      <c r="D22" s="51" t="n">
+      <c r="D22" s="50" t="n">
         <v>46195</v>
       </c>
-      <c r="E22" s="51" t="n">
+      <c r="E22" s="50" t="n">
         <v>46242</v>
       </c>
-      <c r="F22" s="45" t="inlineStr">
+      <c r="F22" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
       </c>
       <c r="G22" s="47" t="n"/>
       <c r="H22" s="47" t="n"/>
-      <c r="I22" s="46" t="n"/>
-      <c r="J22" s="46" t="n"/>
-      <c r="K22" s="46" t="n"/>
-      <c r="L22" s="46" t="n"/>
-      <c r="M22" s="46" t="n"/>
-      <c r="N22" s="55" t="n"/>
-      <c r="O22" s="46" t="n"/>
+      <c r="I22" s="52" t="n"/>
+      <c r="J22" s="52" t="n"/>
+      <c r="K22" s="52" t="n"/>
+      <c r="L22" s="52" t="n"/>
+      <c r="M22" s="52" t="n"/>
+      <c r="N22" s="52" t="n"/>
+      <c r="O22" s="52" t="n"/>
       <c r="P22" s="47" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
@@ -1685,7 +1690,7 @@
       <c r="E23" s="44" t="n">
         <v>46246</v>
       </c>
-      <c r="F23" s="52" t="inlineStr">
+      <c r="F23" s="53" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
@@ -1697,46 +1702,46 @@
       <c r="K23" s="47" t="n"/>
       <c r="L23" s="47" t="n"/>
       <c r="M23" s="47" t="n"/>
-      <c r="N23" s="48" t="n"/>
-      <c r="O23" s="53" t="n"/>
-      <c r="P23" s="53" t="n"/>
+      <c r="N23" s="47" t="n"/>
+      <c r="O23" s="54" t="n"/>
+      <c r="P23" s="54" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="49" t="inlineStr">
+      <c r="A24" s="48" t="inlineStr">
         <is>
           <t>UX-03</t>
         </is>
       </c>
-      <c r="B24" s="50" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>Front-end UI implementation</t>
         </is>
       </c>
-      <c r="C24" s="50" t="inlineStr">
+      <c r="C24" s="49" t="inlineStr">
         <is>
           <t>Mo (A/R); Nick and Dan (C); Tamer (I)</t>
         </is>
       </c>
-      <c r="D24" s="51" t="n">
+      <c r="D24" s="50" t="n">
         <v>46195</v>
       </c>
-      <c r="E24" s="51" t="n">
+      <c r="E24" s="50" t="n">
         <v>46242</v>
       </c>
-      <c r="F24" s="45" t="inlineStr">
+      <c r="F24" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
       </c>
-      <c r="G24" s="46" t="n"/>
-      <c r="H24" s="46" t="n"/>
-      <c r="I24" s="46" t="n"/>
-      <c r="J24" s="46" t="n"/>
-      <c r="K24" s="46" t="n"/>
-      <c r="L24" s="46" t="n"/>
-      <c r="M24" s="46" t="n"/>
-      <c r="N24" s="55" t="n"/>
-      <c r="O24" s="46" t="n"/>
+      <c r="G24" s="47" t="n"/>
+      <c r="H24" s="47" t="n"/>
+      <c r="I24" s="52" t="n"/>
+      <c r="J24" s="52" t="n"/>
+      <c r="K24" s="52" t="n"/>
+      <c r="L24" s="52" t="n"/>
+      <c r="M24" s="52" t="n"/>
+      <c r="N24" s="52" t="n"/>
+      <c r="O24" s="52" t="n"/>
       <c r="P24" s="47" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
@@ -1761,7 +1766,7 @@
       <c r="E25" s="44" t="n">
         <v>46244</v>
       </c>
-      <c r="F25" s="56" t="inlineStr">
+      <c r="F25" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
@@ -1771,49 +1776,49 @@
       <c r="I25" s="47" t="n"/>
       <c r="J25" s="47" t="n"/>
       <c r="K25" s="47" t="n"/>
-      <c r="L25" s="47" t="n"/>
-      <c r="M25" s="47" t="n"/>
-      <c r="N25" s="48" t="n"/>
-      <c r="O25" s="57" t="n"/>
-      <c r="P25" s="57" t="n"/>
+      <c r="L25" s="52" t="n"/>
+      <c r="M25" s="52" t="n"/>
+      <c r="N25" s="52" t="n"/>
+      <c r="O25" s="52" t="n"/>
+      <c r="P25" s="52" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="49" t="inlineStr">
+      <c r="A26" s="48" t="inlineStr">
         <is>
           <t>RISK-01</t>
         </is>
       </c>
-      <c r="B26" s="50" t="inlineStr">
+      <c r="B26" s="49" t="inlineStr">
         <is>
           <t>Legal, regulatory and document research</t>
         </is>
       </c>
-      <c r="C26" s="50" t="inlineStr">
+      <c r="C26" s="49" t="inlineStr">
         <is>
           <t>Badhri (A/R); Tamer (C)</t>
         </is>
       </c>
-      <c r="D26" s="51" t="n">
+      <c r="D26" s="50" t="n">
         <v>46182</v>
       </c>
-      <c r="E26" s="51" t="n">
+      <c r="E26" s="50" t="n">
         <v>46239</v>
       </c>
-      <c r="F26" s="56" t="inlineStr">
+      <c r="F26" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
       </c>
-      <c r="G26" s="57" t="n"/>
-      <c r="H26" s="57" t="n"/>
-      <c r="I26" s="57" t="n"/>
-      <c r="J26" s="57" t="n"/>
-      <c r="K26" s="57" t="n"/>
-      <c r="L26" s="57" t="n"/>
-      <c r="M26" s="57" t="n"/>
-      <c r="N26" s="58" t="n"/>
-      <c r="O26" s="57" t="n"/>
-      <c r="P26" s="57" t="n"/>
+      <c r="G26" s="52" t="n"/>
+      <c r="H26" s="52" t="n"/>
+      <c r="I26" s="52" t="n"/>
+      <c r="J26" s="52" t="n"/>
+      <c r="K26" s="52" t="n"/>
+      <c r="L26" s="52" t="n"/>
+      <c r="M26" s="52" t="n"/>
+      <c r="N26" s="52" t="n"/>
+      <c r="O26" s="52" t="n"/>
+      <c r="P26" s="47" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="42" t="inlineStr">
@@ -1837,59 +1842,59 @@
       <c r="E27" s="44" t="n">
         <v>46246</v>
       </c>
-      <c r="F27" s="56" t="inlineStr">
+      <c r="F27" s="53" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
       </c>
-      <c r="G27" s="57" t="n"/>
-      <c r="H27" s="57" t="n"/>
-      <c r="I27" s="57" t="n"/>
-      <c r="J27" s="57" t="n"/>
-      <c r="K27" s="57" t="n"/>
-      <c r="L27" s="57" t="n"/>
-      <c r="M27" s="57" t="n"/>
-      <c r="N27" s="58" t="n"/>
-      <c r="O27" s="57" t="n"/>
-      <c r="P27" s="57" t="n"/>
+      <c r="G27" s="47" t="n"/>
+      <c r="H27" s="47" t="n"/>
+      <c r="I27" s="47" t="n"/>
+      <c r="J27" s="47" t="n"/>
+      <c r="K27" s="47" t="n"/>
+      <c r="L27" s="47" t="n"/>
+      <c r="M27" s="47" t="n"/>
+      <c r="N27" s="47" t="n"/>
+      <c r="O27" s="54" t="n"/>
+      <c r="P27" s="54" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="49" t="inlineStr">
+      <c r="A28" s="48" t="inlineStr">
         <is>
           <t>BUS-01</t>
         </is>
       </c>
-      <c r="B28" s="50" t="inlineStr">
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>Financial model, pricing and funding assumptions</t>
         </is>
       </c>
-      <c r="C28" s="50" t="inlineStr">
+      <c r="C28" s="49" t="inlineStr">
         <is>
           <t>Conrad (A/R); Mo (R); Tamer (C)</t>
         </is>
       </c>
-      <c r="D28" s="51" t="n">
+      <c r="D28" s="50" t="n">
         <v>46182</v>
       </c>
-      <c r="E28" s="51" t="n">
+      <c r="E28" s="50" t="n">
         <v>46246</v>
       </c>
-      <c r="F28" s="52" t="inlineStr">
+      <c r="F28" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
       </c>
-      <c r="G28" s="47" t="n"/>
-      <c r="H28" s="47" t="n"/>
-      <c r="I28" s="47" t="n"/>
-      <c r="J28" s="47" t="n"/>
-      <c r="K28" s="47" t="n"/>
-      <c r="L28" s="47" t="n"/>
-      <c r="M28" s="47" t="n"/>
-      <c r="N28" s="48" t="n"/>
-      <c r="O28" s="47" t="n"/>
-      <c r="P28" s="53" t="n"/>
+      <c r="G28" s="52" t="n"/>
+      <c r="H28" s="52" t="n"/>
+      <c r="I28" s="52" t="n"/>
+      <c r="J28" s="52" t="n"/>
+      <c r="K28" s="52" t="n"/>
+      <c r="L28" s="52" t="n"/>
+      <c r="M28" s="52" t="n"/>
+      <c r="N28" s="52" t="n"/>
+      <c r="O28" s="52" t="n"/>
+      <c r="P28" s="52" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="42" t="inlineStr">
@@ -1913,45 +1918,45 @@
       <c r="E29" s="44" t="n">
         <v>46246</v>
       </c>
-      <c r="F29" s="52" t="inlineStr">
+      <c r="F29" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
       </c>
-      <c r="G29" s="47" t="n"/>
-      <c r="H29" s="47" t="n"/>
-      <c r="I29" s="47" t="n"/>
-      <c r="J29" s="47" t="n"/>
-      <c r="K29" s="47" t="n"/>
-      <c r="L29" s="47" t="n"/>
-      <c r="M29" s="47" t="n"/>
-      <c r="N29" s="54" t="n"/>
-      <c r="O29" s="53" t="n"/>
-      <c r="P29" s="53" t="n"/>
+      <c r="G29" s="52" t="n"/>
+      <c r="H29" s="52" t="n"/>
+      <c r="I29" s="52" t="n"/>
+      <c r="J29" s="52" t="n"/>
+      <c r="K29" s="52" t="n"/>
+      <c r="L29" s="52" t="n"/>
+      <c r="M29" s="52" t="n"/>
+      <c r="N29" s="52" t="n"/>
+      <c r="O29" s="52" t="n"/>
+      <c r="P29" s="52" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="49" t="inlineStr">
+      <c r="A30" s="48" t="inlineStr">
         <is>
           <t>BUS-03</t>
         </is>
       </c>
-      <c r="B30" s="50" t="inlineStr">
+      <c r="B30" s="49" t="inlineStr">
         <is>
           <t>Business model and commercial narrative</t>
         </is>
       </c>
-      <c r="C30" s="50" t="inlineStr">
+      <c r="C30" s="49" t="inlineStr">
         <is>
           <t>Tamer (A/R); Conrad and Badhri (C)</t>
         </is>
       </c>
-      <c r="D30" s="51" t="n">
+      <c r="D30" s="50" t="n">
         <v>46246</v>
       </c>
-      <c r="E30" s="51" t="n">
+      <c r="E30" s="50" t="n">
         <v>46246</v>
       </c>
-      <c r="F30" s="59" t="inlineStr">
+      <c r="F30" s="53" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
@@ -1963,9 +1968,9 @@
       <c r="K30" s="47" t="n"/>
       <c r="L30" s="47" t="n"/>
       <c r="M30" s="47" t="n"/>
-      <c r="N30" s="48" t="n"/>
-      <c r="O30" s="60" t="n"/>
-      <c r="P30" s="60" t="n"/>
+      <c r="N30" s="47" t="n"/>
+      <c r="O30" s="47" t="n"/>
+      <c r="P30" s="54" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="42" t="inlineStr">
@@ -1989,7 +1994,7 @@
       <c r="E31" s="44" t="n">
         <v>46246</v>
       </c>
-      <c r="F31" s="59" t="inlineStr">
+      <c r="F31" s="51" t="inlineStr">
         <is>
           <t>Doing</t>
         </is>
@@ -2001,33 +2006,33 @@
       <c r="K31" s="47" t="n"/>
       <c r="L31" s="47" t="n"/>
       <c r="M31" s="47" t="n"/>
-      <c r="N31" s="48" t="n"/>
-      <c r="O31" s="47" t="n"/>
-      <c r="P31" s="60" t="n"/>
+      <c r="N31" s="52" t="n"/>
+      <c r="O31" s="52" t="n"/>
+      <c r="P31" s="52" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="49" t="inlineStr">
+      <c r="A32" s="48" t="inlineStr">
         <is>
           <t>SUB-02</t>
         </is>
       </c>
-      <c r="B32" s="50" t="inlineStr">
+      <c r="B32" s="49" t="inlineStr">
         <is>
           <t>Demo runbook</t>
         </is>
       </c>
-      <c r="C32" s="50" t="inlineStr">
+      <c r="C32" s="49" t="inlineStr">
         <is>
           <t>Dan (A/R); Nick (R); Mo (C)</t>
         </is>
       </c>
-      <c r="D32" s="51" t="n">
+      <c r="D32" s="50" t="n">
         <v>46237</v>
       </c>
-      <c r="E32" s="51" t="n">
+      <c r="E32" s="50" t="n">
         <v>46246</v>
       </c>
-      <c r="F32" s="59" t="inlineStr">
+      <c r="F32" s="53" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
@@ -2039,119 +2044,119 @@
       <c r="K32" s="47" t="n"/>
       <c r="L32" s="47" t="n"/>
       <c r="M32" s="47" t="n"/>
-      <c r="N32" s="48" t="n"/>
-      <c r="O32" s="47" t="n"/>
-      <c r="P32" s="60" t="n"/>
+      <c r="N32" s="47" t="n"/>
+      <c r="O32" s="54" t="n"/>
+      <c r="P32" s="54" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="61" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>SUB-03</t>
         </is>
       </c>
-      <c r="B33" s="62" t="inlineStr">
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>Rehearsals and recordings</t>
         </is>
       </c>
-      <c r="C33" s="62" t="inlineStr">
+      <c r="C33" s="43" t="inlineStr">
         <is>
           <t>Dan (A/R); Tamer and Mo (R); Nick (C)</t>
         </is>
       </c>
-      <c r="D33" s="63" t="n">
+      <c r="D33" s="44" t="n">
         <v>46244</v>
       </c>
-      <c r="E33" s="63" t="n">
+      <c r="E33" s="44" t="n">
         <v>46247</v>
       </c>
-      <c r="F33" s="61" t="inlineStr">
+      <c r="F33" s="53" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
       </c>
-      <c r="G33" s="64" t="n"/>
-      <c r="H33" s="64" t="n"/>
-      <c r="I33" s="64" t="n"/>
-      <c r="J33" s="64" t="n"/>
-      <c r="K33" s="64" t="n"/>
-      <c r="L33" s="64" t="n"/>
-      <c r="M33" s="64" t="n"/>
-      <c r="N33" s="65" t="n"/>
-      <c r="O33" s="64" t="n"/>
-      <c r="P33" s="64" t="n"/>
+      <c r="G33" s="47" t="n"/>
+      <c r="H33" s="47" t="n"/>
+      <c r="I33" s="47" t="n"/>
+      <c r="J33" s="47" t="n"/>
+      <c r="K33" s="47" t="n"/>
+      <c r="L33" s="47" t="n"/>
+      <c r="M33" s="47" t="n"/>
+      <c r="N33" s="47" t="n"/>
+      <c r="O33" s="47" t="n"/>
+      <c r="P33" s="54" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="61" t="inlineStr">
+      <c r="A34" s="48" t="inlineStr">
         <is>
           <t>SUB-04</t>
         </is>
       </c>
-      <c r="B34" s="62" t="inlineStr">
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>Submission QA and upload</t>
         </is>
       </c>
-      <c r="C34" s="62" t="inlineStr">
+      <c r="C34" s="49" t="inlineStr">
         <is>
           <t>Tamer (A/R); Dan (R); Mo (C)</t>
         </is>
       </c>
-      <c r="D34" s="63" t="n">
+      <c r="D34" s="50" t="n">
         <v>46247</v>
       </c>
-      <c r="E34" s="63" t="n">
+      <c r="E34" s="50" t="n">
         <v>46248</v>
       </c>
-      <c r="F34" s="61" t="inlineStr">
+      <c r="F34" s="53" t="inlineStr">
         <is>
           <t>To Do</t>
         </is>
       </c>
-      <c r="G34" s="64" t="n"/>
-      <c r="H34" s="64" t="n"/>
-      <c r="I34" s="64" t="n"/>
-      <c r="J34" s="64" t="n"/>
-      <c r="K34" s="64" t="n"/>
-      <c r="L34" s="64" t="n"/>
-      <c r="M34" s="64" t="n"/>
-      <c r="N34" s="65" t="n"/>
-      <c r="O34" s="64" t="n"/>
-      <c r="P34" s="64" t="n"/>
+      <c r="G34" s="47" t="n"/>
+      <c r="H34" s="47" t="n"/>
+      <c r="I34" s="47" t="n"/>
+      <c r="J34" s="47" t="n"/>
+      <c r="K34" s="47" t="n"/>
+      <c r="L34" s="47" t="n"/>
+      <c r="M34" s="47" t="n"/>
+      <c r="N34" s="47" t="n"/>
+      <c r="O34" s="47" t="n"/>
+      <c r="P34" s="54" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="61" t="inlineStr">
+      <c r="A35" s="55" t="inlineStr">
         <is>
           <t>DEF-01</t>
         </is>
       </c>
-      <c r="B35" s="62" t="inlineStr">
+      <c r="B35" s="56" t="inlineStr">
         <is>
           <t>Post-MVP integrations and production hardening</t>
         </is>
       </c>
-      <c r="C35" s="62" t="inlineStr">
+      <c r="C35" s="56" t="inlineStr">
         <is>
           <t>Tamer (A); technical and domain leads (C)</t>
         </is>
       </c>
-      <c r="D35" s="63" t="n"/>
-      <c r="E35" s="63" t="n"/>
-      <c r="F35" s="61" t="inlineStr">
+      <c r="D35" s="57" t="n"/>
+      <c r="E35" s="57" t="n"/>
+      <c r="F35" s="58" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G35" s="64" t="n"/>
-      <c r="H35" s="64" t="n"/>
-      <c r="I35" s="64" t="n"/>
-      <c r="J35" s="64" t="n"/>
-      <c r="K35" s="64" t="n"/>
-      <c r="L35" s="64" t="n"/>
-      <c r="M35" s="64" t="n"/>
-      <c r="N35" s="65" t="n"/>
-      <c r="O35" s="64" t="n"/>
-      <c r="P35" s="64" t="n"/>
+      <c r="G35" s="55" t="n"/>
+      <c r="H35" s="55" t="n"/>
+      <c r="I35" s="55" t="n"/>
+      <c r="J35" s="55" t="n"/>
+      <c r="K35" s="55" t="n"/>
+      <c r="L35" s="55" t="n"/>
+      <c r="M35" s="55" t="n"/>
+      <c r="N35" s="55" t="n"/>
+      <c r="O35" s="55" t="n"/>
+      <c r="P35" s="55" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A8:P35"/>
@@ -2224,6 +2229,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing ns1:id="anysvml"/>
 </worksheet>
 </file>